--- a/artfynd/A 3958-2024 artfynd.xlsx
+++ b/artfynd/A 3958-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979888</v>
+        <v>130979945</v>
       </c>
       <c r="B2" t="n">
         <v>57884</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590692</v>
+        <v>590594</v>
       </c>
       <c r="R2" t="n">
-        <v>6963278</v>
+        <v>6963385</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130979927</v>
+        <v>130979888</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590832</v>
+        <v>590692</v>
       </c>
       <c r="R3" t="n">
-        <v>6963235</v>
+        <v>6963278</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979945</v>
+        <v>130979927</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590594</v>
+        <v>590832</v>
       </c>
       <c r="R4" t="n">
-        <v>6963385</v>
+        <v>6963235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1035,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130979891</v>
+        <v>130979933</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590710</v>
+        <v>590658</v>
       </c>
       <c r="R5" t="n">
-        <v>6963217</v>
+        <v>6963312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130979933</v>
+        <v>130979891</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590658</v>
+        <v>590710</v>
       </c>
       <c r="R6" t="n">
-        <v>6963312</v>
+        <v>6963217</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1712,7 +1712,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130979934</v>
+        <v>130979928</v>
       </c>
       <c r="B11" t="n">
         <v>57884</v>
@@ -1745,7 +1745,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590655</v>
+        <v>590813</v>
       </c>
       <c r="R11" t="n">
-        <v>6963332</v>
+        <v>6963212</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1952,7 +1952,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130979928</v>
+        <v>130979934</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -1985,7 +1985,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590813</v>
+        <v>590655</v>
       </c>
       <c r="R13" t="n">
-        <v>6963212</v>
+        <v>6963332</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,12 +2040,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,7 +2072,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130979929</v>
+        <v>130979889</v>
       </c>
       <c r="B14" t="n">
         <v>57884</v>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590797</v>
+        <v>590701</v>
       </c>
       <c r="R14" t="n">
-        <v>6963219</v>
+        <v>6963240</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,7 +2192,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130979889</v>
+        <v>130979929</v>
       </c>
       <c r="B15" t="n">
         <v>57884</v>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590701</v>
+        <v>590797</v>
       </c>
       <c r="R15" t="n">
-        <v>6963240</v>
+        <v>6963219</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,7 +2312,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130979895</v>
+        <v>130979948</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590687</v>
+        <v>590579</v>
       </c>
       <c r="R16" t="n">
-        <v>6963193</v>
+        <v>6963330</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,7 +2432,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130979948</v>
+        <v>130979895</v>
       </c>
       <c r="B17" t="n">
         <v>57884</v>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590579</v>
+        <v>590687</v>
       </c>
       <c r="R17" t="n">
-        <v>6963330</v>
+        <v>6963193</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130979899</v>
+        <v>130979897</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>80348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2670,42 +2670,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590850</v>
+        <v>590726</v>
       </c>
       <c r="R19" t="n">
-        <v>6963133</v>
+        <v>6963153</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2737,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,12 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2899,10 +2886,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130979897</v>
+        <v>130979899</v>
       </c>
       <c r="B21" t="n">
-        <v>80348</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2910,34 +2897,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590726</v>
+        <v>590850</v>
       </c>
       <c r="R21" t="n">
-        <v>6963153</v>
+        <v>6963133</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2969,7 +2964,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2979,7 +2974,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3126,7 +3126,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130979944</v>
+        <v>130979923</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590599</v>
+        <v>590913</v>
       </c>
       <c r="R23" t="n">
-        <v>6963388</v>
+        <v>6963246</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3246,7 +3246,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130979923</v>
+        <v>130979944</v>
       </c>
       <c r="B24" t="n">
         <v>57884</v>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590913</v>
+        <v>590599</v>
       </c>
       <c r="R24" t="n">
-        <v>6963246</v>
+        <v>6963388</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3366,7 +3366,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130979890</v>
+        <v>130979925</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590704</v>
+        <v>590855</v>
       </c>
       <c r="R25" t="n">
-        <v>6963217</v>
+        <v>6963228</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3454,12 +3454,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3486,7 +3486,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130979900</v>
+        <v>130979890</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590843</v>
+        <v>590704</v>
       </c>
       <c r="R26" t="n">
-        <v>6963130</v>
+        <v>6963217</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3606,7 +3606,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130979925</v>
+        <v>130979900</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590855</v>
+        <v>590843</v>
       </c>
       <c r="R27" t="n">
-        <v>6963228</v>
+        <v>6963130</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3966,7 +3966,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130979930</v>
+        <v>130979932</v>
       </c>
       <c r="B30" t="n">
         <v>57884</v>
@@ -3999,7 +3999,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>590789</v>
+        <v>590660</v>
       </c>
       <c r="R30" t="n">
-        <v>6963216</v>
+        <v>6963313</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4086,7 +4086,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130979932</v>
+        <v>130979930</v>
       </c>
       <c r="B31" t="n">
         <v>57884</v>
@@ -4119,7 +4119,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4129,10 +4129,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590660</v>
+        <v>590789</v>
       </c>
       <c r="R31" t="n">
-        <v>6963313</v>
+        <v>6963216</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4206,7 +4206,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130979898</v>
+        <v>130979893</v>
       </c>
       <c r="B32" t="n">
         <v>57884</v>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590830</v>
+        <v>590717</v>
       </c>
       <c r="R32" t="n">
-        <v>6963134</v>
+        <v>6963211</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4446,7 +4446,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130979893</v>
+        <v>130979898</v>
       </c>
       <c r="B34" t="n">
         <v>57884</v>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590717</v>
+        <v>590830</v>
       </c>
       <c r="R34" t="n">
-        <v>6963211</v>
+        <v>6963134</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">

--- a/artfynd/A 3958-2024 artfynd.xlsx
+++ b/artfynd/A 3958-2024 artfynd.xlsx
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130979897</v>
+        <v>130979946</v>
       </c>
       <c r="B19" t="n">
-        <v>80348</v>
+        <v>57884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2670,34 +2670,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590726</v>
+        <v>590605</v>
       </c>
       <c r="R19" t="n">
-        <v>6963153</v>
+        <v>6963364</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2729,7 +2737,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2747,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2766,7 +2779,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130979946</v>
+        <v>130979899</v>
       </c>
       <c r="B20" t="n">
         <v>57884</v>
@@ -2809,10 +2822,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590605</v>
+        <v>590850</v>
       </c>
       <c r="R20" t="n">
-        <v>6963364</v>
+        <v>6963133</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2844,7 +2857,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2854,7 +2867,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2886,10 +2899,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130979899</v>
+        <v>130979897</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>80348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2897,42 +2910,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590850</v>
+        <v>590726</v>
       </c>
       <c r="R21" t="n">
-        <v>6963133</v>
+        <v>6963153</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2964,7 +2969,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2974,12 +2979,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130979893</v>
+        <v>130979941</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>79243</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4217,42 +4217,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590717</v>
+        <v>590615</v>
       </c>
       <c r="R32" t="n">
-        <v>6963211</v>
+        <v>6963396</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4284,7 +4276,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4294,12 +4286,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4326,7 +4313,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130979943</v>
+        <v>130979893</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -4369,10 +4356,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590608</v>
+        <v>590717</v>
       </c>
       <c r="R33" t="n">
-        <v>6963380</v>
+        <v>6963211</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4404,7 +4391,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4414,7 +4401,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4446,7 +4433,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130979898</v>
+        <v>130979943</v>
       </c>
       <c r="B34" t="n">
         <v>57884</v>
@@ -4489,10 +4476,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590830</v>
+        <v>590608</v>
       </c>
       <c r="R34" t="n">
-        <v>6963134</v>
+        <v>6963380</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4524,7 +4511,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4534,7 +4521,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4566,10 +4553,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130979941</v>
+        <v>130979898</v>
       </c>
       <c r="B35" t="n">
-        <v>79243</v>
+        <v>57884</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4577,34 +4564,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590615</v>
+        <v>590830</v>
       </c>
       <c r="R35" t="n">
-        <v>6963396</v>
+        <v>6963134</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4636,7 +4631,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4646,7 +4641,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 3958-2024 artfynd.xlsx
+++ b/artfynd/A 3958-2024 artfynd.xlsx
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130979935</v>
+        <v>130979926</v>
       </c>
       <c r="B8" t="n">
-        <v>91828</v>
+        <v>79244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,19 +1406,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1426,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590645</v>
+        <v>590852</v>
       </c>
       <c r="R8" t="n">
-        <v>6963341</v>
+        <v>6963248</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1465,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1475,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130979926</v>
+        <v>130979935</v>
       </c>
       <c r="B9" t="n">
-        <v>79243</v>
+        <v>91829</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,23 +1513,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590852</v>
+        <v>590645</v>
       </c>
       <c r="R9" t="n">
-        <v>6963248</v>
+        <v>6963341</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,7 +1608,7 @@
         <v>130979924</v>
       </c>
       <c r="B10" t="n">
-        <v>80348</v>
+        <v>80349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>130979947</v>
       </c>
       <c r="B18" t="n">
-        <v>91808</v>
+        <v>91809</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130979946</v>
+        <v>130979897</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2670,42 +2670,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590605</v>
+        <v>590726</v>
       </c>
       <c r="R19" t="n">
-        <v>6963364</v>
+        <v>6963153</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2737,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,12 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2779,7 +2766,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130979899</v>
+        <v>130979946</v>
       </c>
       <c r="B20" t="n">
         <v>57884</v>
@@ -2822,10 +2809,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590850</v>
+        <v>590605</v>
       </c>
       <c r="R20" t="n">
-        <v>6963133</v>
+        <v>6963364</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2857,7 +2844,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2867,7 +2854,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2899,10 +2886,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130979897</v>
+        <v>130979899</v>
       </c>
       <c r="B21" t="n">
-        <v>80348</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2910,34 +2897,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590726</v>
+        <v>590850</v>
       </c>
       <c r="R21" t="n">
-        <v>6963153</v>
+        <v>6963133</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2969,7 +2964,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2979,7 +2974,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4209,7 +4209,7 @@
         <v>130979941</v>
       </c>
       <c r="B32" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 3958-2024 artfynd.xlsx
+++ b/artfynd/A 3958-2024 artfynd.xlsx
@@ -4206,10 +4206,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130979941</v>
+        <v>130979893</v>
       </c>
       <c r="B32" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4217,34 +4217,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590615</v>
+        <v>590717</v>
       </c>
       <c r="R32" t="n">
-        <v>6963396</v>
+        <v>6963211</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4276,7 +4284,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4286,7 +4294,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4313,7 +4326,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130979893</v>
+        <v>130979943</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -4356,10 +4369,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590717</v>
+        <v>590608</v>
       </c>
       <c r="R33" t="n">
-        <v>6963211</v>
+        <v>6963380</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4391,7 +4404,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4401,7 +4414,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4433,7 +4446,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130979943</v>
+        <v>130979898</v>
       </c>
       <c r="B34" t="n">
         <v>57884</v>
@@ -4476,10 +4489,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590608</v>
+        <v>590830</v>
       </c>
       <c r="R34" t="n">
-        <v>6963380</v>
+        <v>6963134</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4511,7 +4524,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4521,7 +4534,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4553,10 +4566,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130979898</v>
+        <v>130979941</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4564,42 +4577,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590830</v>
+        <v>590615</v>
       </c>
       <c r="R35" t="n">
-        <v>6963134</v>
+        <v>6963396</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4631,7 +4636,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4641,12 +4646,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 3958-2024 artfynd.xlsx
+++ b/artfynd/A 3958-2024 artfynd.xlsx
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130979926</v>
+        <v>130979935</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>91829</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,23 +1406,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1430,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590852</v>
+        <v>590645</v>
       </c>
       <c r="R8" t="n">
-        <v>6963248</v>
+        <v>6963341</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130979935</v>
+        <v>130979926</v>
       </c>
       <c r="B9" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,19 +1509,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590645</v>
+        <v>590852</v>
       </c>
       <c r="R9" t="n">
-        <v>6963341</v>
+        <v>6963248</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2552,10 +2552,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130979947</v>
+        <v>130979897</v>
       </c>
       <c r="B18" t="n">
-        <v>91809</v>
+        <v>80349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2563,21 +2563,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590591</v>
+        <v>590726</v>
       </c>
       <c r="R18" t="n">
-        <v>6963354</v>
+        <v>6963153</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130979897</v>
+        <v>130979947</v>
       </c>
       <c r="B19" t="n">
-        <v>80349</v>
+        <v>91809</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2670,21 +2670,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2694,10 +2694,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590726</v>
+        <v>590591</v>
       </c>
       <c r="R19" t="n">
-        <v>6963153</v>
+        <v>6963354</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3126,7 +3126,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130979923</v>
+        <v>130979944</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590913</v>
+        <v>590599</v>
       </c>
       <c r="R23" t="n">
-        <v>6963246</v>
+        <v>6963388</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3246,7 +3246,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130979944</v>
+        <v>130979923</v>
       </c>
       <c r="B24" t="n">
         <v>57884</v>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590599</v>
+        <v>590913</v>
       </c>
       <c r="R24" t="n">
-        <v>6963388</v>
+        <v>6963246</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130979893</v>
+        <v>130979941</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4217,42 +4217,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590717</v>
+        <v>590615</v>
       </c>
       <c r="R32" t="n">
-        <v>6963211</v>
+        <v>6963396</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4284,7 +4276,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4294,12 +4286,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4326,7 +4313,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130979943</v>
+        <v>130979893</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -4369,10 +4356,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590608</v>
+        <v>590717</v>
       </c>
       <c r="R33" t="n">
-        <v>6963380</v>
+        <v>6963211</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4404,7 +4391,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4414,7 +4401,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4446,7 +4433,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130979898</v>
+        <v>130979943</v>
       </c>
       <c r="B34" t="n">
         <v>57884</v>
@@ -4489,10 +4476,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590830</v>
+        <v>590608</v>
       </c>
       <c r="R34" t="n">
-        <v>6963134</v>
+        <v>6963380</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4524,7 +4511,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4534,7 +4521,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4566,10 +4553,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130979941</v>
+        <v>130979898</v>
       </c>
       <c r="B35" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4577,34 +4564,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590615</v>
+        <v>590830</v>
       </c>
       <c r="R35" t="n">
-        <v>6963396</v>
+        <v>6963134</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4636,7 +4631,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4646,7 +4641,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 3958-2024 artfynd.xlsx
+++ b/artfynd/A 3958-2024 artfynd.xlsx
@@ -2552,10 +2552,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130979897</v>
+        <v>130979947</v>
       </c>
       <c r="B18" t="n">
-        <v>80349</v>
+        <v>91809</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2563,21 +2563,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590726</v>
+        <v>590591</v>
       </c>
       <c r="R18" t="n">
-        <v>6963153</v>
+        <v>6963354</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130979947</v>
+        <v>130979897</v>
       </c>
       <c r="B19" t="n">
-        <v>91809</v>
+        <v>80349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2670,21 +2670,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2694,10 +2694,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590591</v>
+        <v>590726</v>
       </c>
       <c r="R19" t="n">
-        <v>6963354</v>
+        <v>6963153</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3126,7 +3126,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130979944</v>
+        <v>130979923</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590599</v>
+        <v>590913</v>
       </c>
       <c r="R23" t="n">
-        <v>6963388</v>
+        <v>6963246</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3246,7 +3246,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130979923</v>
+        <v>130979944</v>
       </c>
       <c r="B24" t="n">
         <v>57884</v>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590913</v>
+        <v>590599</v>
       </c>
       <c r="R24" t="n">
-        <v>6963246</v>
+        <v>6963388</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130979941</v>
+        <v>130979893</v>
       </c>
       <c r="B32" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4217,34 +4217,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590615</v>
+        <v>590717</v>
       </c>
       <c r="R32" t="n">
-        <v>6963396</v>
+        <v>6963211</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4276,7 +4284,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4286,7 +4294,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4313,7 +4326,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130979893</v>
+        <v>130979943</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -4356,10 +4369,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590717</v>
+        <v>590608</v>
       </c>
       <c r="R33" t="n">
-        <v>6963211</v>
+        <v>6963380</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4391,7 +4404,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4401,7 +4414,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4433,7 +4446,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130979943</v>
+        <v>130979898</v>
       </c>
       <c r="B34" t="n">
         <v>57884</v>
@@ -4476,10 +4489,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590608</v>
+        <v>590830</v>
       </c>
       <c r="R34" t="n">
-        <v>6963380</v>
+        <v>6963134</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4511,7 +4524,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4521,7 +4534,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4553,10 +4566,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130979898</v>
+        <v>130979941</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4564,42 +4577,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590830</v>
+        <v>590615</v>
       </c>
       <c r="R35" t="n">
-        <v>6963134</v>
+        <v>6963396</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4631,7 +4636,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4641,12 +4646,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 3958-2024 artfynd.xlsx
+++ b/artfynd/A 3958-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979945</v>
+        <v>130979888</v>
       </c>
       <c r="B2" t="n">
         <v>57884</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590594</v>
+        <v>590692</v>
       </c>
       <c r="R2" t="n">
-        <v>6963385</v>
+        <v>6963278</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130979888</v>
+        <v>130979927</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590692</v>
+        <v>590832</v>
       </c>
       <c r="R3" t="n">
-        <v>6963278</v>
+        <v>6963235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979927</v>
+        <v>130979945</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590832</v>
+        <v>590594</v>
       </c>
       <c r="R4" t="n">
-        <v>6963235</v>
+        <v>6963385</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1035,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130979933</v>
+        <v>130979891</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590658</v>
+        <v>590710</v>
       </c>
       <c r="R5" t="n">
-        <v>6963312</v>
+        <v>6963217</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130979891</v>
+        <v>130979887</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590710</v>
+        <v>590601</v>
       </c>
       <c r="R6" t="n">
-        <v>6963217</v>
+        <v>6963311</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130979887</v>
+        <v>130979933</v>
       </c>
       <c r="B7" t="n">
         <v>57884</v>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590601</v>
+        <v>590658</v>
       </c>
       <c r="R7" t="n">
-        <v>6963311</v>
+        <v>6963312</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130979935</v>
+        <v>130979926</v>
       </c>
       <c r="B8" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,19 +1406,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1426,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590645</v>
+        <v>590852</v>
       </c>
       <c r="R8" t="n">
-        <v>6963341</v>
+        <v>6963248</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1465,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1475,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130979926</v>
+        <v>130979935</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>91829</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,23 +1513,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590852</v>
+        <v>590645</v>
       </c>
       <c r="R9" t="n">
-        <v>6963248</v>
+        <v>6963341</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1712,7 +1712,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130979928</v>
+        <v>130979934</v>
       </c>
       <c r="B11" t="n">
         <v>57884</v>
@@ -1745,7 +1745,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590813</v>
+        <v>590655</v>
       </c>
       <c r="R11" t="n">
-        <v>6963212</v>
+        <v>6963332</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1952,7 +1952,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130979934</v>
+        <v>130979928</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -1985,7 +1985,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590655</v>
+        <v>590813</v>
       </c>
       <c r="R13" t="n">
-        <v>6963332</v>
+        <v>6963212</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,12 +2040,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,7 +2072,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130979889</v>
+        <v>130979929</v>
       </c>
       <c r="B14" t="n">
         <v>57884</v>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590701</v>
+        <v>590797</v>
       </c>
       <c r="R14" t="n">
-        <v>6963240</v>
+        <v>6963219</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,7 +2192,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130979929</v>
+        <v>130979889</v>
       </c>
       <c r="B15" t="n">
         <v>57884</v>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590797</v>
+        <v>590701</v>
       </c>
       <c r="R15" t="n">
-        <v>6963219</v>
+        <v>6963240</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,7 +2312,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130979948</v>
+        <v>130979895</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590579</v>
+        <v>590687</v>
       </c>
       <c r="R16" t="n">
-        <v>6963330</v>
+        <v>6963193</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,7 +2432,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130979895</v>
+        <v>130979948</v>
       </c>
       <c r="B17" t="n">
         <v>57884</v>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590687</v>
+        <v>590579</v>
       </c>
       <c r="R17" t="n">
-        <v>6963193</v>
+        <v>6963330</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2766,7 +2766,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130979946</v>
+        <v>130979899</v>
       </c>
       <c r="B20" t="n">
         <v>57884</v>
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590605</v>
+        <v>590850</v>
       </c>
       <c r="R20" t="n">
-        <v>6963364</v>
+        <v>6963133</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2886,7 +2886,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130979899</v>
+        <v>130979946</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590850</v>
+        <v>590605</v>
       </c>
       <c r="R21" t="n">
-        <v>6963133</v>
+        <v>6963364</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3126,7 +3126,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130979923</v>
+        <v>130979944</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590913</v>
+        <v>590599</v>
       </c>
       <c r="R23" t="n">
-        <v>6963246</v>
+        <v>6963388</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3246,7 +3246,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130979944</v>
+        <v>130979923</v>
       </c>
       <c r="B24" t="n">
         <v>57884</v>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590599</v>
+        <v>590913</v>
       </c>
       <c r="R24" t="n">
-        <v>6963388</v>
+        <v>6963246</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3366,7 +3366,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130979925</v>
+        <v>130979890</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590855</v>
+        <v>590704</v>
       </c>
       <c r="R25" t="n">
-        <v>6963228</v>
+        <v>6963217</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3454,12 +3454,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3486,7 +3486,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130979890</v>
+        <v>130979900</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590704</v>
+        <v>590843</v>
       </c>
       <c r="R26" t="n">
-        <v>6963217</v>
+        <v>6963130</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3606,7 +3606,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130979900</v>
+        <v>130979925</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590843</v>
+        <v>590855</v>
       </c>
       <c r="R27" t="n">
-        <v>6963130</v>
+        <v>6963228</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3966,7 +3966,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130979932</v>
+        <v>130979930</v>
       </c>
       <c r="B30" t="n">
         <v>57884</v>
@@ -3999,7 +3999,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>590660</v>
+        <v>590789</v>
       </c>
       <c r="R30" t="n">
-        <v>6963313</v>
+        <v>6963216</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4086,7 +4086,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130979930</v>
+        <v>130979932</v>
       </c>
       <c r="B31" t="n">
         <v>57884</v>
@@ -4119,7 +4119,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4129,10 +4129,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590789</v>
+        <v>590660</v>
       </c>
       <c r="R31" t="n">
-        <v>6963216</v>
+        <v>6963313</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130979893</v>
+        <v>130979941</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4217,42 +4217,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590717</v>
+        <v>590615</v>
       </c>
       <c r="R32" t="n">
-        <v>6963211</v>
+        <v>6963396</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4284,7 +4276,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4294,12 +4286,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4326,7 +4313,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130979943</v>
+        <v>130979893</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -4369,10 +4356,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590608</v>
+        <v>590717</v>
       </c>
       <c r="R33" t="n">
-        <v>6963380</v>
+        <v>6963211</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4404,7 +4391,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4414,7 +4401,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4566,10 +4553,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130979941</v>
+        <v>130979943</v>
       </c>
       <c r="B35" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4577,34 +4564,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590615</v>
+        <v>590608</v>
       </c>
       <c r="R35" t="n">
-        <v>6963396</v>
+        <v>6963380</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4636,7 +4631,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4646,7 +4641,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 3958-2024 artfynd.xlsx
+++ b/artfynd/A 3958-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979888</v>
+        <v>130979945</v>
       </c>
       <c r="B2" t="n">
         <v>57884</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590692</v>
+        <v>590594</v>
       </c>
       <c r="R2" t="n">
-        <v>6963278</v>
+        <v>6963385</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130979927</v>
+        <v>130979888</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590832</v>
+        <v>590692</v>
       </c>
       <c r="R3" t="n">
-        <v>6963235</v>
+        <v>6963278</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979945</v>
+        <v>130979927</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590594</v>
+        <v>590832</v>
       </c>
       <c r="R4" t="n">
-        <v>6963385</v>
+        <v>6963235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1035,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130979891</v>
+        <v>130979933</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590710</v>
+        <v>590658</v>
       </c>
       <c r="R5" t="n">
-        <v>6963217</v>
+        <v>6963312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130979887</v>
+        <v>130979891</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590601</v>
+        <v>590710</v>
       </c>
       <c r="R6" t="n">
-        <v>6963311</v>
+        <v>6963217</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130979933</v>
+        <v>130979887</v>
       </c>
       <c r="B7" t="n">
         <v>57884</v>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590658</v>
+        <v>590601</v>
       </c>
       <c r="R7" t="n">
-        <v>6963312</v>
+        <v>6963311</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130979926</v>
+        <v>130979935</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>91830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,23 +1406,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1430,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590852</v>
+        <v>590645</v>
       </c>
       <c r="R8" t="n">
-        <v>6963248</v>
+        <v>6963341</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130979935</v>
+        <v>130979926</v>
       </c>
       <c r="B9" t="n">
-        <v>91829</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,19 +1509,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590645</v>
+        <v>590852</v>
       </c>
       <c r="R9" t="n">
-        <v>6963341</v>
+        <v>6963248</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,7 +1608,7 @@
         <v>130979924</v>
       </c>
       <c r="B10" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130979934</v>
+        <v>130979928</v>
       </c>
       <c r="B11" t="n">
         <v>57884</v>
@@ -1745,7 +1745,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590655</v>
+        <v>590813</v>
       </c>
       <c r="R11" t="n">
-        <v>6963332</v>
+        <v>6963212</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1952,7 +1952,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130979928</v>
+        <v>130979934</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -1985,7 +1985,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590813</v>
+        <v>590655</v>
       </c>
       <c r="R13" t="n">
-        <v>6963212</v>
+        <v>6963332</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,12 +2040,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,7 +2072,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130979929</v>
+        <v>130979889</v>
       </c>
       <c r="B14" t="n">
         <v>57884</v>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590797</v>
+        <v>590701</v>
       </c>
       <c r="R14" t="n">
-        <v>6963219</v>
+        <v>6963240</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,7 +2192,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130979889</v>
+        <v>130979929</v>
       </c>
       <c r="B15" t="n">
         <v>57884</v>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590701</v>
+        <v>590797</v>
       </c>
       <c r="R15" t="n">
-        <v>6963240</v>
+        <v>6963219</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,7 +2312,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130979895</v>
+        <v>130979948</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590687</v>
+        <v>590579</v>
       </c>
       <c r="R16" t="n">
-        <v>6963193</v>
+        <v>6963330</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,7 +2432,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130979948</v>
+        <v>130979895</v>
       </c>
       <c r="B17" t="n">
         <v>57884</v>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590579</v>
+        <v>590687</v>
       </c>
       <c r="R17" t="n">
-        <v>6963330</v>
+        <v>6963193</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,10 +2552,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130979947</v>
+        <v>130979897</v>
       </c>
       <c r="B18" t="n">
-        <v>91809</v>
+        <v>80350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2563,21 +2563,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590591</v>
+        <v>590726</v>
       </c>
       <c r="R18" t="n">
-        <v>6963354</v>
+        <v>6963153</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130979897</v>
+        <v>130979947</v>
       </c>
       <c r="B19" t="n">
-        <v>80349</v>
+        <v>91810</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2670,21 +2670,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2694,10 +2694,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590726</v>
+        <v>590591</v>
       </c>
       <c r="R19" t="n">
-        <v>6963153</v>
+        <v>6963354</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2766,7 +2766,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130979899</v>
+        <v>130979946</v>
       </c>
       <c r="B20" t="n">
         <v>57884</v>
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590850</v>
+        <v>590605</v>
       </c>
       <c r="R20" t="n">
-        <v>6963133</v>
+        <v>6963364</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2886,7 +2886,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130979946</v>
+        <v>130979899</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590605</v>
+        <v>590850</v>
       </c>
       <c r="R21" t="n">
-        <v>6963364</v>
+        <v>6963133</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3126,7 +3126,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130979944</v>
+        <v>130979923</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590599</v>
+        <v>590913</v>
       </c>
       <c r="R23" t="n">
-        <v>6963388</v>
+        <v>6963246</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3246,7 +3246,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130979923</v>
+        <v>130979944</v>
       </c>
       <c r="B24" t="n">
         <v>57884</v>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590913</v>
+        <v>590599</v>
       </c>
       <c r="R24" t="n">
-        <v>6963246</v>
+        <v>6963388</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3366,7 +3366,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130979890</v>
+        <v>130979925</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590704</v>
+        <v>590855</v>
       </c>
       <c r="R25" t="n">
-        <v>6963217</v>
+        <v>6963228</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3454,12 +3454,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3486,7 +3486,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130979900</v>
+        <v>130979890</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590843</v>
+        <v>590704</v>
       </c>
       <c r="R26" t="n">
-        <v>6963130</v>
+        <v>6963217</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3606,7 +3606,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130979925</v>
+        <v>130979900</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590855</v>
+        <v>590843</v>
       </c>
       <c r="R27" t="n">
-        <v>6963228</v>
+        <v>6963130</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4209,7 +4209,7 @@
         <v>130979941</v>
       </c>
       <c r="B32" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130979893</v>
+        <v>130979943</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -4356,10 +4356,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590717</v>
+        <v>590608</v>
       </c>
       <c r="R33" t="n">
-        <v>6963211</v>
+        <v>6963380</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4553,7 +4553,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130979943</v>
+        <v>130979893</v>
       </c>
       <c r="B35" t="n">
         <v>57884</v>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590608</v>
+        <v>590717</v>
       </c>
       <c r="R35" t="n">
-        <v>6963380</v>
+        <v>6963211</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">

--- a/artfynd/A 3958-2024 artfynd.xlsx
+++ b/artfynd/A 3958-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979945</v>
+        <v>130979927</v>
       </c>
       <c r="B2" t="n">
         <v>57884</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590594</v>
+        <v>590832</v>
       </c>
       <c r="R2" t="n">
-        <v>6963385</v>
+        <v>6963235</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130979888</v>
+        <v>130979945</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590692</v>
+        <v>590594</v>
       </c>
       <c r="R3" t="n">
-        <v>6963278</v>
+        <v>6963385</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979927</v>
+        <v>130979888</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590832</v>
+        <v>590692</v>
       </c>
       <c r="R4" t="n">
-        <v>6963235</v>
+        <v>6963278</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2312,7 +2312,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130979948</v>
+        <v>130979895</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590579</v>
+        <v>590687</v>
       </c>
       <c r="R16" t="n">
-        <v>6963330</v>
+        <v>6963193</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,7 +2432,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130979895</v>
+        <v>130979948</v>
       </c>
       <c r="B17" t="n">
         <v>57884</v>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590687</v>
+        <v>590579</v>
       </c>
       <c r="R17" t="n">
-        <v>6963193</v>
+        <v>6963330</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3966,7 +3966,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130979930</v>
+        <v>130979932</v>
       </c>
       <c r="B30" t="n">
         <v>57884</v>
@@ -3999,7 +3999,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>590789</v>
+        <v>590660</v>
       </c>
       <c r="R30" t="n">
-        <v>6963216</v>
+        <v>6963313</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4086,7 +4086,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130979932</v>
+        <v>130979930</v>
       </c>
       <c r="B31" t="n">
         <v>57884</v>
@@ -4119,7 +4119,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4129,10 +4129,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590660</v>
+        <v>590789</v>
       </c>
       <c r="R31" t="n">
-        <v>6963313</v>
+        <v>6963216</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 3958-2024 artfynd.xlsx
+++ b/artfynd/A 3958-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979927</v>
+        <v>130979945</v>
       </c>
       <c r="B2" t="n">
         <v>57884</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590832</v>
+        <v>590594</v>
       </c>
       <c r="R2" t="n">
-        <v>6963235</v>
+        <v>6963385</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130979945</v>
+        <v>130979888</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590594</v>
+        <v>590692</v>
       </c>
       <c r="R3" t="n">
-        <v>6963385</v>
+        <v>6963278</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979888</v>
+        <v>130979927</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590692</v>
+        <v>590832</v>
       </c>
       <c r="R4" t="n">
-        <v>6963278</v>
+        <v>6963235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3958-2024 artfynd.xlsx
+++ b/artfynd/A 3958-2024 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>130979935</v>
       </c>
       <c r="B8" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130979895</v>
+        <v>130979948</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590687</v>
+        <v>590579</v>
       </c>
       <c r="R16" t="n">
-        <v>6963193</v>
+        <v>6963330</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,7 +2432,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130979948</v>
+        <v>130979895</v>
       </c>
       <c r="B17" t="n">
         <v>57884</v>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590579</v>
+        <v>590687</v>
       </c>
       <c r="R17" t="n">
-        <v>6963330</v>
+        <v>6963193</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,10 +2552,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130979897</v>
+        <v>130979947</v>
       </c>
       <c r="B18" t="n">
-        <v>80350</v>
+        <v>91813</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2563,21 +2563,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590726</v>
+        <v>590591</v>
       </c>
       <c r="R18" t="n">
-        <v>6963153</v>
+        <v>6963354</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130979947</v>
+        <v>130979897</v>
       </c>
       <c r="B19" t="n">
-        <v>91810</v>
+        <v>80350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2670,21 +2670,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2694,10 +2694,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590591</v>
+        <v>590726</v>
       </c>
       <c r="R19" t="n">
-        <v>6963354</v>
+        <v>6963153</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3486,7 +3486,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130979890</v>
+        <v>130979900</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590704</v>
+        <v>590843</v>
       </c>
       <c r="R26" t="n">
-        <v>6963217</v>
+        <v>6963130</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3606,7 +3606,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130979900</v>
+        <v>130979890</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590843</v>
+        <v>590704</v>
       </c>
       <c r="R27" t="n">
-        <v>6963130</v>
+        <v>6963217</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130979941</v>
+        <v>130979893</v>
       </c>
       <c r="B32" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4217,34 +4217,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590615</v>
+        <v>590717</v>
       </c>
       <c r="R32" t="n">
-        <v>6963396</v>
+        <v>6963211</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4276,7 +4284,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4286,7 +4294,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4553,10 +4566,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130979893</v>
+        <v>130979941</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4564,42 +4577,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590717</v>
+        <v>590615</v>
       </c>
       <c r="R35" t="n">
-        <v>6963211</v>
+        <v>6963396</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4631,7 +4636,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4641,12 +4646,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 3958-2024 artfynd.xlsx
+++ b/artfynd/A 3958-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979945</v>
+        <v>130979927</v>
       </c>
       <c r="B2" t="n">
         <v>57884</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590594</v>
+        <v>590832</v>
       </c>
       <c r="R2" t="n">
-        <v>6963385</v>
+        <v>6963235</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979927</v>
+        <v>130979945</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590832</v>
+        <v>590594</v>
       </c>
       <c r="R4" t="n">
-        <v>6963235</v>
+        <v>6963385</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1035,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130979933</v>
+        <v>130979891</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590658</v>
+        <v>590710</v>
       </c>
       <c r="R5" t="n">
-        <v>6963312</v>
+        <v>6963217</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130979891</v>
+        <v>130979887</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590710</v>
+        <v>590601</v>
       </c>
       <c r="R6" t="n">
-        <v>6963217</v>
+        <v>6963311</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130979887</v>
+        <v>130979933</v>
       </c>
       <c r="B7" t="n">
         <v>57884</v>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590601</v>
+        <v>590658</v>
       </c>
       <c r="R7" t="n">
-        <v>6963311</v>
+        <v>6963312</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1398,7 +1398,7 @@
         <v>130979935</v>
       </c>
       <c r="B8" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>130979926</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>130979924</v>
       </c>
       <c r="B10" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130979937</v>
+        <v>130979934</v>
       </c>
       <c r="B12" t="n">
         <v>57884</v>
@@ -1865,7 +1865,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590635</v>
+        <v>590655</v>
       </c>
       <c r="R12" t="n">
-        <v>6963366</v>
+        <v>6963332</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,7 +1952,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130979934</v>
+        <v>130979937</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -1985,7 +1985,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590655</v>
+        <v>590635</v>
       </c>
       <c r="R13" t="n">
-        <v>6963332</v>
+        <v>6963366</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,12 +2040,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2312,7 +2312,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130979948</v>
+        <v>130979895</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590579</v>
+        <v>590687</v>
       </c>
       <c r="R16" t="n">
-        <v>6963330</v>
+        <v>6963193</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,7 +2432,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130979895</v>
+        <v>130979948</v>
       </c>
       <c r="B17" t="n">
         <v>57884</v>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590687</v>
+        <v>590579</v>
       </c>
       <c r="R17" t="n">
-        <v>6963193</v>
+        <v>6963330</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2555,7 +2555,7 @@
         <v>130979947</v>
       </c>
       <c r="B18" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130979897</v>
+        <v>130979899</v>
       </c>
       <c r="B19" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2670,34 +2670,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590726</v>
+        <v>590850</v>
       </c>
       <c r="R19" t="n">
-        <v>6963153</v>
+        <v>6963133</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2729,7 +2737,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2747,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2886,10 +2899,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130979899</v>
+        <v>130979897</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2897,42 +2910,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590850</v>
+        <v>590726</v>
       </c>
       <c r="R21" t="n">
-        <v>6963133</v>
+        <v>6963153</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2964,7 +2969,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2974,12 +2979,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3126,7 +3126,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130979923</v>
+        <v>130979944</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590913</v>
+        <v>590599</v>
       </c>
       <c r="R23" t="n">
-        <v>6963246</v>
+        <v>6963388</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3246,7 +3246,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130979944</v>
+        <v>130979923</v>
       </c>
       <c r="B24" t="n">
         <v>57884</v>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590599</v>
+        <v>590913</v>
       </c>
       <c r="R24" t="n">
-        <v>6963388</v>
+        <v>6963246</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3486,7 +3486,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130979900</v>
+        <v>130979890</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590843</v>
+        <v>590704</v>
       </c>
       <c r="R26" t="n">
-        <v>6963130</v>
+        <v>6963217</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3606,7 +3606,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130979890</v>
+        <v>130979900</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590704</v>
+        <v>590843</v>
       </c>
       <c r="R27" t="n">
-        <v>6963217</v>
+        <v>6963130</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130979893</v>
+        <v>130979941</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4217,42 +4217,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590717</v>
+        <v>590615</v>
       </c>
       <c r="R32" t="n">
-        <v>6963211</v>
+        <v>6963396</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4284,7 +4276,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4294,12 +4286,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4326,7 +4313,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130979943</v>
+        <v>130979898</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -4369,10 +4356,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590608</v>
+        <v>590830</v>
       </c>
       <c r="R33" t="n">
-        <v>6963380</v>
+        <v>6963134</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4404,7 +4391,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4414,7 +4401,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4446,7 +4433,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130979898</v>
+        <v>130979943</v>
       </c>
       <c r="B34" t="n">
         <v>57884</v>
@@ -4489,10 +4476,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590830</v>
+        <v>590608</v>
       </c>
       <c r="R34" t="n">
-        <v>6963134</v>
+        <v>6963380</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4524,7 +4511,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4534,7 +4521,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4566,10 +4553,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130979941</v>
+        <v>130979893</v>
       </c>
       <c r="B35" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4577,34 +4564,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590615</v>
+        <v>590717</v>
       </c>
       <c r="R35" t="n">
-        <v>6963396</v>
+        <v>6963211</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4636,7 +4631,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4646,7 +4641,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 3958-2024 artfynd.xlsx
+++ b/artfynd/A 3958-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979927</v>
+        <v>130979947</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590832</v>
+        <v>590591</v>
       </c>
       <c r="R2" t="n">
-        <v>6963235</v>
+        <v>6963354</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,53 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130979888</v>
+        <v>130979926</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590692</v>
+        <v>590852</v>
       </c>
       <c r="R3" t="n">
-        <v>6963278</v>
+        <v>6963248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,53 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979945</v>
+        <v>130979941</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590594</v>
+        <v>590615</v>
       </c>
       <c r="R4" t="n">
-        <v>6963385</v>
+        <v>6963396</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130979891</v>
+        <v>130979897</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,42 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590710</v>
+        <v>590726</v>
       </c>
       <c r="R5" t="n">
-        <v>6963217</v>
+        <v>6963153</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130979887</v>
+        <v>130979924</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,42 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590601</v>
+        <v>590895</v>
       </c>
       <c r="R6" t="n">
-        <v>6963311</v>
+        <v>6963262</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130979933</v>
+        <v>130979887</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590658</v>
+        <v>590601</v>
       </c>
       <c r="R7" t="n">
-        <v>6963312</v>
+        <v>6963311</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1298,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1395,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130979935</v>
+        <v>130979888</v>
       </c>
       <c r="B8" t="n">
-        <v>91834</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,30 +1341,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590645</v>
+        <v>590692</v>
       </c>
       <c r="R8" t="n">
-        <v>6963341</v>
+        <v>6963278</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1408,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1418,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130979926</v>
+        <v>130979889</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,34 +1461,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590852</v>
+        <v>590701</v>
       </c>
       <c r="R9" t="n">
-        <v>6963248</v>
+        <v>6963240</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1538,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130979924</v>
+        <v>130979890</v>
       </c>
       <c r="B10" t="n">
-        <v>80351</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,34 +1581,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590895</v>
+        <v>590704</v>
       </c>
       <c r="R10" t="n">
-        <v>6963262</v>
+        <v>6963217</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1648,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1658,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130979928</v>
+        <v>130979891</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590813</v>
+        <v>590710</v>
       </c>
       <c r="R11" t="n">
-        <v>6963212</v>
+        <v>6963217</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1832,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130979934</v>
+        <v>130979893</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1843,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1875,10 +1853,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590655</v>
+        <v>590717</v>
       </c>
       <c r="R12" t="n">
-        <v>6963332</v>
+        <v>6963211</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1888,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,12 +1898,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130979937</v>
+        <v>130979894</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590635</v>
+        <v>590712</v>
       </c>
       <c r="R13" t="n">
-        <v>6963366</v>
+        <v>6963209</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,12 +2018,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130979889</v>
+        <v>130979895</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,10 +2093,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590701</v>
+        <v>590687</v>
       </c>
       <c r="R14" t="n">
-        <v>6963240</v>
+        <v>6963193</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2150,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2160,12 +2138,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130979929</v>
+        <v>130979898</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,10 +2213,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590797</v>
+        <v>590830</v>
       </c>
       <c r="R15" t="n">
-        <v>6963219</v>
+        <v>6963134</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2270,7 +2248,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,7 +2258,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2312,10 +2290,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130979895</v>
+        <v>130979899</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,10 +2333,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590687</v>
+        <v>590850</v>
       </c>
       <c r="R16" t="n">
-        <v>6963193</v>
+        <v>6963133</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2390,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2400,7 +2378,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2432,10 +2410,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130979948</v>
+        <v>130979900</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,10 +2453,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590579</v>
+        <v>590843</v>
       </c>
       <c r="R17" t="n">
-        <v>6963330</v>
+        <v>6963130</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2510,7 +2488,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2520,12 +2498,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,10 +2530,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130979947</v>
+        <v>130979921</v>
       </c>
       <c r="B18" t="n">
-        <v>91814</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2563,34 +2541,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590591</v>
+        <v>590951</v>
       </c>
       <c r="R18" t="n">
-        <v>6963354</v>
+        <v>6963242</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2622,7 +2608,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2632,7 +2618,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,10 +2650,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130979899</v>
+        <v>130979922</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2702,10 +2693,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590850</v>
+        <v>590936</v>
       </c>
       <c r="R19" t="n">
-        <v>6963133</v>
+        <v>6963244</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2737,7 +2728,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,7 +2738,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2779,10 +2770,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130979946</v>
+        <v>130979923</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,10 +2813,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590605</v>
+        <v>590913</v>
       </c>
       <c r="R20" t="n">
-        <v>6963364</v>
+        <v>6963246</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2857,7 +2848,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2867,7 +2858,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2899,10 +2890,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130979897</v>
+        <v>130979925</v>
       </c>
       <c r="B21" t="n">
-        <v>80351</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2910,34 +2901,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590726</v>
+        <v>590855</v>
       </c>
       <c r="R21" t="n">
-        <v>6963153</v>
+        <v>6963228</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2969,7 +2968,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2979,7 +2978,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3006,10 +3010,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130979931</v>
+        <v>130979927</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3049,10 +3053,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590690</v>
+        <v>590832</v>
       </c>
       <c r="R22" t="n">
-        <v>6963301</v>
+        <v>6963235</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3084,7 +3088,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3094,7 +3098,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3126,10 +3130,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130979944</v>
+        <v>130979928</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,10 +3173,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590599</v>
+        <v>590813</v>
       </c>
       <c r="R23" t="n">
-        <v>6963388</v>
+        <v>6963212</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3204,7 +3208,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3214,7 +3218,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3246,10 +3250,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130979923</v>
+        <v>130979929</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3289,10 +3293,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590913</v>
+        <v>590797</v>
       </c>
       <c r="R24" t="n">
-        <v>6963246</v>
+        <v>6963219</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3324,7 +3328,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3334,7 +3338,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3366,10 +3370,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130979925</v>
+        <v>130979930</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3399,7 +3403,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3409,10 +3413,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590855</v>
+        <v>590789</v>
       </c>
       <c r="R25" t="n">
-        <v>6963228</v>
+        <v>6963216</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3444,7 +3448,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3454,12 +3458,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3486,10 +3490,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130979890</v>
+        <v>130979931</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3529,10 +3533,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590704</v>
+        <v>590690</v>
       </c>
       <c r="R26" t="n">
-        <v>6963217</v>
+        <v>6963301</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3564,7 +3568,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3574,7 +3578,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3606,10 +3610,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130979900</v>
+        <v>130979932</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3649,10 +3653,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590843</v>
+        <v>590660</v>
       </c>
       <c r="R27" t="n">
-        <v>6963130</v>
+        <v>6963313</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3684,7 +3688,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3694,12 +3698,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3726,10 +3730,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130979894</v>
+        <v>130979933</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3769,10 +3773,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>590712</v>
+        <v>590658</v>
       </c>
       <c r="R28" t="n">
-        <v>6963209</v>
+        <v>6963312</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3804,7 +3808,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3814,12 +3818,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3846,10 +3850,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130979936</v>
+        <v>130979934</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3879,7 +3883,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3889,10 +3893,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>590647</v>
+        <v>590655</v>
       </c>
       <c r="R29" t="n">
-        <v>6963338</v>
+        <v>6963332</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3924,7 +3928,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3934,12 +3938,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre sannolikt bohål i grantickerötad gran. Omkring 1.5 meter ovan mark. Bohålsdiametern är ungefär 4.5 cm. I lämplig biotop för arten.</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3966,10 +3970,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130979932</v>
+        <v>130979936</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3999,7 +4003,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4009,10 +4013,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>590660</v>
+        <v>590647</v>
       </c>
       <c r="R30" t="n">
-        <v>6963313</v>
+        <v>6963338</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4044,7 +4048,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4054,12 +4058,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>Äldre sannolikt bohål i grantickerötad gran. Omkring 1.5 meter ovan mark. Bohålsdiametern är ungefär 4.5 cm. I lämplig biotop för arten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4086,10 +4090,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130979930</v>
+        <v>130979937</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4119,7 +4123,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4129,10 +4133,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590789</v>
+        <v>590635</v>
       </c>
       <c r="R31" t="n">
-        <v>6963216</v>
+        <v>6963366</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4164,7 +4168,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4174,12 +4178,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4206,10 +4210,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130979941</v>
+        <v>130979939</v>
       </c>
       <c r="B32" t="n">
-        <v>79246</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4217,34 +4221,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590615</v>
+        <v>590592</v>
       </c>
       <c r="R32" t="n">
-        <v>6963396</v>
+        <v>6963412</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4276,7 +4288,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4286,7 +4298,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4313,10 +4330,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130979898</v>
+        <v>130979940</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4356,10 +4373,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590830</v>
+        <v>590594</v>
       </c>
       <c r="R33" t="n">
-        <v>6963134</v>
+        <v>6963404</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4391,7 +4408,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4401,12 +4418,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4436,7 +4453,7 @@
         <v>130979943</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4553,10 +4570,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130979893</v>
+        <v>130979944</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4596,10 +4613,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590717</v>
+        <v>590599</v>
       </c>
       <c r="R35" t="n">
-        <v>6963211</v>
+        <v>6963388</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4631,7 +4648,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4641,7 +4658,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4670,6 +4687,366 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130979945</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>590594</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6963385</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130979946</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>590605</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6963364</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130979948</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>590579</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6963330</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3958-2024 artfynd.xlsx
+++ b/artfynd/A 3958-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979947</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979926</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979941</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979897</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979924</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979887</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979888</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1567,6 +1607,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979889</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1687,6 +1732,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979890</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1807,6 +1857,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979891</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1927,6 +1982,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979893</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2047,6 +2107,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979894</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2167,6 +2232,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979895</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2287,6 +2357,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979898</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2407,6 +2482,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979899</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2527,6 +2607,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979900</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2647,6 +2732,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979921</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2767,6 +2857,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979922</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2887,6 +2982,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979923</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3007,6 +3107,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979925</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3127,6 +3232,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979927</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3247,6 +3357,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979928</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3367,6 +3482,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979929</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3487,6 +3607,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979930</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3607,6 +3732,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979931</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3727,6 +3857,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979932</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3847,6 +3982,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979933</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3967,6 +4107,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979934</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4087,6 +4232,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979936</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4207,6 +4357,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979937</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4327,6 +4482,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979939</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4447,6 +4607,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979940</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4567,6 +4732,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979943</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4687,6 +4857,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979944</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4807,6 +4982,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979945</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4927,6 +5107,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979946</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5047,8 +5232,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979948</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>